--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_12.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03391851949538459</v>
+        <v>0.02978995995856105</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008468882373272653</v>
+        <v>0.008460309764744066</v>
       </c>
       <c r="C2" t="n">
-        <v>76356972</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>76356972</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>50833204</v>
+        <v>3974833</v>
       </c>
       <c r="L2" t="n">
-        <v>25504606</v>
+        <v>1617865</v>
       </c>
       <c r="M2" t="n">
-        <v>5592343</v>
+        <v>274133</v>
       </c>
       <c r="N2" t="n">
-        <v>237000</v>
+        <v>5246</v>
       </c>
       <c r="O2" t="n">
-        <v>3350461</v>
+        <v>156074</v>
       </c>
       <c r="P2" t="n">
-        <v>1205974</v>
+        <v>1862</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999842643737793</v>
+        <v>0.9999667406082153</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8011264801025391</v>
+        <v>0.7033125758171082</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6482343673706055</v>
+        <v>0.5146136283874512</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5631125569343567</v>
+        <v>0.3763355910778046</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1762347817420959</v>
+        <v>0.03885983675718307</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6109026670455933</v>
+        <v>0.3839562833309174</v>
       </c>
       <c r="W2" t="n">
-        <v>0.756109356880188</v>
+        <v>0.4582820534706116</v>
       </c>
       <c r="X2" t="n">
-        <v>76356972</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>76356972</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>57941310</v>
+        <v>4760658</v>
       </c>
       <c r="AG2" t="n">
-        <v>36227525</v>
+        <v>3049090</v>
       </c>
       <c r="AH2" t="n">
-        <v>9662257</v>
+        <v>809872</v>
       </c>
       <c r="AI2" t="n">
-        <v>711841</v>
+        <v>59470</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5526744</v>
+        <v>462174</v>
       </c>
       <c r="AK2" t="n">
-        <v>2163347</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9556514024734497</v>
+        <v>0.9542856216430664</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9117959141731262</v>
+        <v>0.9129269123077393</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8578110933303833</v>
+        <v>0.857567310333252</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6610904335975647</v>
+        <v>0.6599931120872498</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9018860459327698</v>
+        <v>0.9016656875610352</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314352869987488</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.009108619579805096</v>
+        <v>0.007845845769742541</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002028431794565072</v>
+        <v>0.002026924819488894</v>
       </c>
       <c r="C3" t="n">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>50833204</v>
+        <v>3974833</v>
       </c>
       <c r="E3" t="n">
-        <v>9272179</v>
+        <v>947315</v>
       </c>
       <c r="F3" t="n">
-        <v>340077</v>
+        <v>41988</v>
       </c>
       <c r="G3" t="n">
-        <v>40741</v>
+        <v>4188</v>
       </c>
       <c r="H3" t="n">
-        <v>28477</v>
+        <v>4183</v>
       </c>
       <c r="I3" t="n">
-        <v>1618</v>
+        <v>110</v>
       </c>
       <c r="J3" t="n">
-        <v>121152227</v>
+        <v>10069409</v>
       </c>
       <c r="K3" t="n">
-        <v>124375046</v>
+        <v>9766611</v>
       </c>
       <c r="L3" t="n">
-        <v>143846594</v>
+        <v>11536568</v>
       </c>
       <c r="M3" t="n">
-        <v>181892627</v>
+        <v>15015581</v>
       </c>
       <c r="N3" t="n">
-        <v>195324685</v>
+        <v>16196012</v>
       </c>
       <c r="O3" t="n">
-        <v>189243514</v>
+        <v>15652463</v>
       </c>
       <c r="P3" t="n">
-        <v>194797867</v>
+        <v>16219749</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8399905562400818</v>
+        <v>0.7993415594100952</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6404381394386292</v>
+        <v>0.4824475049972534</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4958195686340332</v>
+        <v>0.2897428870201111</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2198683023452759</v>
+        <v>0.05813644081354141</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5463090538978577</v>
+        <v>0.3041654825210571</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5190257430076599</v>
+        <v>0.009595464915037155</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57941310</v>
+        <v>4760658</v>
       </c>
       <c r="Z3" t="n">
-        <v>2388917</v>
+        <v>196517</v>
       </c>
       <c r="AA3" t="n">
-        <v>102998</v>
+        <v>8569</v>
       </c>
       <c r="AB3" t="n">
-        <v>82445</v>
+        <v>6849</v>
       </c>
       <c r="AC3" t="n">
-        <v>370</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>121153428</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>134305137</v>
+        <v>11215310</v>
       </c>
       <c r="AG3" t="n">
-        <v>154182186</v>
+        <v>12771731</v>
       </c>
       <c r="AH3" t="n">
-        <v>184629817</v>
+        <v>15335364</v>
       </c>
       <c r="AI3" t="n">
-        <v>196067555</v>
+        <v>16295127</v>
       </c>
       <c r="AJ3" t="n">
-        <v>190776255</v>
+        <v>15852474</v>
       </c>
       <c r="AK3" t="n">
-        <v>195027618</v>
+        <v>16208628</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9574480652809143</v>
+        <v>0.9573714733123779</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9096980094909668</v>
+        <v>0.9092389345169067</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8566599488258362</v>
+        <v>0.8559883832931519</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6603851318359375</v>
+        <v>0.6590496301651001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9011626243591309</v>
+        <v>0.9007097482681274</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9310588836669922</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.07361034102924312</v>
+        <v>0.06591330473716989</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0320094986107273</v>
+        <v>0.03198862993387096</v>
       </c>
       <c r="C4" t="n">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>11512060</v>
+        <v>1480964</v>
       </c>
       <c r="E4" t="n">
-        <v>25504606</v>
+        <v>1617865</v>
       </c>
       <c r="F4" t="n">
-        <v>2299072</v>
+        <v>199387</v>
       </c>
       <c r="G4" t="n">
-        <v>183308</v>
+        <v>21173</v>
       </c>
       <c r="H4" t="n">
-        <v>298651</v>
+        <v>33676</v>
       </c>
       <c r="I4" t="n">
-        <v>25888</v>
+        <v>383</v>
       </c>
       <c r="J4" t="n">
-        <v>1201</v>
+        <v>211</v>
       </c>
       <c r="K4" t="n">
-        <v>12618954</v>
+        <v>1676755</v>
       </c>
       <c r="L4" t="n">
-        <v>13840122</v>
+        <v>1525979</v>
       </c>
       <c r="M4" t="n">
-        <v>4338785</v>
+        <v>454294</v>
       </c>
       <c r="N4" t="n">
-        <v>1107797</v>
+        <v>129752</v>
       </c>
       <c r="O4" t="n">
-        <v>2133982</v>
+        <v>250415</v>
       </c>
       <c r="P4" t="n">
-        <v>388999</v>
+        <v>2201</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999921321868896</v>
+        <v>0.9999833703041077</v>
       </c>
       <c r="R4" t="n">
-        <v>0.820098340511322</v>
+        <v>0.748258650302887</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6443126797676086</v>
+        <v>0.4980117082595825</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5273278951644897</v>
+        <v>0.3274105489253998</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1956482827663422</v>
+        <v>0.0465826652944088</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5768030881881714</v>
+        <v>0.3394348323345184</v>
       </c>
       <c r="W4" t="n">
-        <v>0.615527331829071</v>
+        <v>0.01879735291004181</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2511522</v>
+        <v>213160</v>
       </c>
       <c r="Z4" t="n">
-        <v>36227525</v>
+        <v>3049090</v>
       </c>
       <c r="AA4" t="n">
-        <v>1002730</v>
+        <v>84162</v>
       </c>
       <c r="AB4" t="n">
-        <v>67105</v>
+        <v>5695</v>
       </c>
       <c r="AC4" t="n">
-        <v>13976</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>826</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2688863</v>
+        <v>228056</v>
       </c>
       <c r="AG4" t="n">
-        <v>3504530</v>
+        <v>290816</v>
       </c>
       <c r="AH4" t="n">
-        <v>1601595</v>
+        <v>134511</v>
       </c>
       <c r="AI4" t="n">
-        <v>364927</v>
+        <v>30637</v>
       </c>
       <c r="AJ4" t="n">
-        <v>601241</v>
+        <v>50404</v>
       </c>
       <c r="AK4" t="n">
-        <v>159248</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9565488696098328</v>
+        <v>0.9558260440826416</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107457995414734</v>
+        <v>0.9110792279243469</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8572351336479187</v>
+        <v>0.8567771315574646</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6607376337051392</v>
+        <v>0.6595210433006287</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9015241861343384</v>
+        <v>0.9011874794960022</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312470555305481</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>159</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>800195</v>
+        <v>144474</v>
       </c>
       <c r="E5" t="n">
-        <v>3578221</v>
+        <v>416499</v>
       </c>
       <c r="F5" t="n">
-        <v>5592343</v>
+        <v>274133</v>
       </c>
       <c r="G5" t="n">
-        <v>342402</v>
+        <v>34209</v>
       </c>
       <c r="H5" t="n">
-        <v>880602</v>
+        <v>76308</v>
       </c>
       <c r="I5" t="n">
-        <v>85066</v>
+        <v>485</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9683196</v>
+        <v>997801</v>
       </c>
       <c r="L5" t="n">
-        <v>14319078</v>
+        <v>1735588</v>
       </c>
       <c r="M5" t="n">
-        <v>5686645</v>
+        <v>671992</v>
       </c>
       <c r="N5" t="n">
-        <v>840918</v>
+        <v>84990</v>
       </c>
       <c r="O5" t="n">
-        <v>2782443</v>
+        <v>357048</v>
       </c>
       <c r="P5" t="n">
-        <v>1117560</v>
+        <v>192188</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999939203262329</v>
+        <v>0.9999871253967285</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8870836496353149</v>
+        <v>0.8370762467384338</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8574292659759521</v>
+        <v>0.8013178110122681</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9492409825325012</v>
+        <v>0.9313909411430359</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9901335835456848</v>
+        <v>0.9869187474250793</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9751080274581909</v>
+        <v>0.9629956483840942</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9923722743988037</v>
+        <v>0.9881585836410522</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>97782</v>
+        <v>8204</v>
       </c>
       <c r="Z5" t="n">
-        <v>1040083</v>
+        <v>87997</v>
       </c>
       <c r="AA5" t="n">
-        <v>9662257</v>
+        <v>809872</v>
       </c>
       <c r="AB5" t="n">
-        <v>120231</v>
+        <v>10066</v>
       </c>
       <c r="AC5" t="n">
-        <v>351023</v>
+        <v>29345</v>
       </c>
       <c r="AD5" t="n">
-        <v>7612</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2575090</v>
+        <v>211976</v>
       </c>
       <c r="AG5" t="n">
-        <v>3596159</v>
+        <v>304363</v>
       </c>
       <c r="AH5" t="n">
-        <v>1616731</v>
+        <v>136253</v>
       </c>
       <c r="AI5" t="n">
-        <v>366077</v>
+        <v>30766</v>
       </c>
       <c r="AJ5" t="n">
-        <v>606160</v>
+        <v>50948</v>
       </c>
       <c r="AK5" t="n">
-        <v>160187</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9733484983444214</v>
+        <v>0.97319495677948</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9640490412712097</v>
+        <v>0.9637439846992493</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837055206298828</v>
+        <v>0.9835060834884644</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962989091873169</v>
+        <v>0.9962595701217651</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938868880271912</v>
+        <v>0.9938260316848755</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983826875686646</v>
+        <v>0.9983697533607483</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>198800</v>
+        <v>24885</v>
       </c>
       <c r="E6" t="n">
-        <v>254656</v>
+        <v>28932</v>
       </c>
       <c r="F6" t="n">
-        <v>259998</v>
+        <v>23226</v>
       </c>
       <c r="G6" t="n">
-        <v>237000</v>
+        <v>5246</v>
       </c>
       <c r="H6" t="n">
-        <v>114668</v>
+        <v>7812</v>
       </c>
       <c r="I6" t="n">
-        <v>12649</v>
+        <v>117</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78965</v>
+        <v>6656</v>
       </c>
       <c r="Z6" t="n">
-        <v>64825</v>
+        <v>5410</v>
       </c>
       <c r="AA6" t="n">
-        <v>132325</v>
+        <v>11168</v>
       </c>
       <c r="AB6" t="n">
-        <v>711841</v>
+        <v>59470</v>
       </c>
       <c r="AC6" t="n">
-        <v>84179</v>
+        <v>7046</v>
       </c>
       <c r="AD6" t="n">
-        <v>5783</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>310</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>99383</v>
+        <v>23983</v>
       </c>
       <c r="E7" t="n">
-        <v>661425</v>
+        <v>117673</v>
       </c>
       <c r="F7" t="n">
-        <v>1292723</v>
+        <v>159109</v>
       </c>
       <c r="G7" t="n">
-        <v>464824</v>
+        <v>55134</v>
       </c>
       <c r="H7" t="n">
-        <v>3350461</v>
+        <v>156074</v>
       </c>
       <c r="I7" t="n">
-        <v>263778</v>
+        <v>1106</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>256</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9731</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>359557</v>
+        <v>30278</v>
       </c>
       <c r="AB7" t="n">
-        <v>91949</v>
+        <v>7760</v>
       </c>
       <c r="AC7" t="n">
-        <v>5526744</v>
+        <v>462174</v>
       </c>
       <c r="AD7" t="n">
-        <v>144667</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>111</v>
       </c>
       <c r="D8" t="n">
-        <v>8516</v>
+        <v>2449</v>
       </c>
       <c r="E8" t="n">
-        <v>73641</v>
+        <v>15560</v>
       </c>
       <c r="F8" t="n">
-        <v>146915</v>
+        <v>30584</v>
       </c>
       <c r="G8" t="n">
-        <v>76522</v>
+        <v>15048</v>
       </c>
       <c r="H8" t="n">
-        <v>811584</v>
+        <v>128436</v>
       </c>
       <c r="I8" t="n">
-        <v>1205974</v>
+        <v>1862</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>338</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>974</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3985</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3197</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151693</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2163347</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
